--- a/bm/MH/ISO.BM-MH-08-01 Phiếu nhập kho vật tư.xlsx
+++ b/bm/MH/ISO.BM-MH-08-01 Phiếu nhập kho vật tư.xlsx
@@ -63,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -85,11 +85,110 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -119,6 +218,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -485,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -500,53 +611,53 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>CÔNG TY QS TECHNOLOGY</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Mã số: ISO.BM-MH-08-01</t>
         </is>
       </c>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
+      <c r="H1" s="12" t="n"/>
+      <c r="I1" s="12" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="A2" s="12" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>Ngày ban hành: 15/06/2026</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Lần ban hành: 01</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -558,36 +669,36 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Số phiếu:  ________________________________</t>
+          <t>Số phiếu:  ................................</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Ngày nhập:  ________________________________</t>
+          <t>Ngày nhập:  ................................</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Nhà cung cấp:  ________________________________</t>
+          <t>Nhà cung cấp:  ................................</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Số HĐ/PO:  ________________________________</t>
+          <t>Số HĐ/PO:  ................................</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Người giao:  ________________________________</t>
+          <t>Người giao:  ................................</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Nhập tại kho:  ________________________________</t>
+          <t>Nhập tại kho:  ................................</t>
         </is>
       </c>
     </row>
@@ -732,6 +843,13 @@
           <t>TỔNG CỘNG:</t>
         </is>
       </c>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="16" t="n"/>
     </row>
     <row r="18" ht="10" customHeight="1"/>
     <row r="19">
@@ -793,31 +911,31 @@
     <row r="23" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="E3:I3"/>
     <mergeCell ref="A20"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="B20"/>
-    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A6:E6"/>
     <mergeCell ref="A19"/>
-    <mergeCell ref="A6:E6"/>
     <mergeCell ref="C19"/>
     <mergeCell ref="A21:I21"/>
-    <mergeCell ref="F7:J7"/>
     <mergeCell ref="D20"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="F5:J5"/>
     <mergeCell ref="D19"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="F6:I6"/>
     <mergeCell ref="C20"/>
+    <mergeCell ref="F7:I7"/>
     <mergeCell ref="E20"/>
-    <mergeCell ref="E2:I2"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="E19"/>
+    <mergeCell ref="F5:I5"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A1:F3"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
